--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104727_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104727_W30.xlsx
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.6355</v>
+        <v>4.6828</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3751</v>
+        <v>3.4977</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2604</v>
+        <v>1.1852</v>
       </c>
       <c r="G2" t="n">
-        <v>3.3085</v>
+        <v>3.2963</v>
       </c>
       <c r="H2" t="n">
-        <v>-2.5966</v>
+        <v>-2.6037</v>
       </c>
       <c r="I2" t="n">
-        <v>5.9051</v>
+        <v>5.9001</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1218</v>
+        <v>5.0997</v>
       </c>
       <c r="K2" t="n">
-        <v>-1.6574</v>
+        <v>-1.6697</v>
       </c>
       <c r="L2" t="n">
-        <v>6.7792</v>
+        <v>6.7694</v>
       </c>
       <c r="M2" t="n">
-        <v>-1.8133</v>
+        <v>-1.8034</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9392</v>
+        <v>-0.9340000000000001</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.8741</v>
+        <v>-0.8694</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.4991</v>
+        <v>2.5039</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.6052</v>
+        <v>0.4564</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.1799</v>
+        <v>-0.0283</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5747</v>
+        <v>0.4846</v>
       </c>
       <c r="V2" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="W2" t="n">
-        <v>0.705</v>
+        <v>0.7025</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.6788</v>
+        <v>3.9486</v>
       </c>
       <c r="E3" t="n">
-        <v>2.9022</v>
+        <v>3.9611</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2234</v>
+        <v>-0.0125</v>
       </c>
       <c r="G3" t="n">
-        <v>3.5631</v>
+        <v>3.5624</v>
       </c>
       <c r="H3" t="n">
-        <v>1.5838</v>
+        <v>1.5825</v>
       </c>
       <c r="I3" t="n">
-        <v>1.9792</v>
+        <v>1.9799</v>
       </c>
       <c r="J3" t="n">
-        <v>5.7671</v>
+        <v>5.7539</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3871</v>
+        <v>3.3784</v>
       </c>
       <c r="L3" t="n">
-        <v>2.38</v>
+        <v>2.3755</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.204</v>
+        <v>-2.1915</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8033</v>
+        <v>-1.7959</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.4008</v>
+        <v>-0.3956</v>
       </c>
       <c r="P3" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q3" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R3" t="n">
-        <v>2.7262</v>
+        <v>2.7316</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1119</v>
+        <v>0.1601</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.4575</v>
+        <v>-0.3768</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3457</v>
+        <v>0.5369</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.2268</v>
+        <v>-0.2292</v>
       </c>
       <c r="W3" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8603</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="4">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.6986</v>
+        <v>1.8466</v>
       </c>
       <c r="E4" t="n">
-        <v>1.7549</v>
+        <v>1.9471</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0563</v>
+        <v>-0.1005</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2711</v>
+        <v>1.2709</v>
       </c>
       <c r="H4" t="n">
-        <v>1.6725</v>
+        <v>1.6715</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.4014</v>
+        <v>-0.4006</v>
       </c>
       <c r="J4" t="n">
-        <v>3.1266</v>
+        <v>3.1164</v>
       </c>
       <c r="K4" t="n">
-        <v>2.2811</v>
+        <v>2.2753</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8455</v>
+        <v>0.8411</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.8555</v>
+        <v>-1.8455</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6086</v>
+        <v>-0.6037</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.2469</v>
+        <v>-1.2417</v>
       </c>
       <c r="P4" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1322</v>
+        <v>1.2798</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5367</v>
+        <v>0.7428</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5955</v>
+        <v>0.5369</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W4" t="n">
-        <v>-0.7724</v>
+        <v>-0.7739</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="5">
@@ -799,58 +799,58 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2763</v>
+        <v>1.2323</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0287</v>
+        <v>-0.0941</v>
       </c>
       <c r="F5" t="n">
-        <v>1.305</v>
+        <v>1.3263</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.3709</v>
+        <v>-0.368</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5726</v>
+        <v>-1.5686</v>
       </c>
       <c r="I5" t="n">
-        <v>1.2017</v>
+        <v>1.2006</v>
       </c>
       <c r="J5" t="n">
-        <v>0.9175</v>
+        <v>0.9076</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7491</v>
+        <v>0.7444</v>
       </c>
       <c r="L5" t="n">
-        <v>0.1684</v>
+        <v>0.1632</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.2885</v>
+        <v>-1.2756</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.3217</v>
+        <v>-2.313</v>
       </c>
       <c r="O5" t="n">
-        <v>1.0332</v>
+        <v>1.0374</v>
       </c>
       <c r="P5" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R5" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S5" t="n">
-        <v>0.5113</v>
+        <v>0.4621</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1897</v>
+        <v>0.1365</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3216</v>
+        <v>0.3256</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.2703</v>
+        <v>-0.1</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5286</v>
+        <v>0.124</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2583</v>
+        <v>-0.224</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.0128</v>
+        <v>-0.0116</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.1706</v>
+        <v>-0.1696</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0173</v>
+        <v>0.0172</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.0301</v>
+        <v>-0.0289</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1878</v>
+        <v>-0.1868</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1578</v>
+        <v>0.1579</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.4544</v>
+        <v>0.4553</v>
       </c>
       <c r="S6" t="n">
-        <v>0.3743</v>
+        <v>0.0011</v>
       </c>
       <c r="T6" t="n">
-        <v>0.5113</v>
+        <v>0.1067</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.137</v>
+        <v>-0.1057</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>O. BALCEROWSKI</t>
+          <t>J. BARREIRO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1258</v>
+        <v>-0.464</v>
       </c>
       <c r="E7" t="n">
-        <v>2.9437</v>
+        <v>0.5790999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.8179</v>
+        <v>-1.0431</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.5138</v>
+        <v>-2.0168</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.3832</v>
+        <v>-0.5376</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8695000000000001</v>
+        <v>-1.4792</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7146</v>
+        <v>-0.6262</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.0683</v>
+        <v>0.0517</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7829</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-1.2284</v>
+        <v>-1.3906</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.3149</v>
+        <v>-0.5893</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0866</v>
+        <v>-0.8012</v>
       </c>
       <c r="P7" t="n">
-        <v>2.0447</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0447</v>
+        <v>0.2276</v>
       </c>
       <c r="S7" t="n">
-        <v>1.6847</v>
+        <v>0.0779</v>
       </c>
       <c r="T7" t="n">
-        <v>2.0451</v>
+        <v>-0.0419</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3604</v>
+        <v>0.1198</v>
       </c>
       <c r="V7" t="n">
-        <v>-3.0897</v>
+        <v>1.2472</v>
       </c>
       <c r="W7" t="n">
-        <v>0.184</v>
+        <v>1.2472</v>
       </c>
       <c r="X7" t="n">
-        <v>-3.2738</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>J. BARREIRO</t>
+          <t>C. DUARTE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6165</v>
+        <v>-0.485</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2784</v>
+        <v>0.5192</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.8949</v>
+        <v>-1.0042</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.0217</v>
+        <v>-1.207</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5417999999999999</v>
+        <v>-0.7435</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.4799</v>
+        <v>-0.4635</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6252</v>
+        <v>0.5835</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0518</v>
+        <v>-0.1831</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6771</v>
+        <v>0.7665999999999999</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.3965</v>
+        <v>-1.7906</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.5936</v>
+        <v>-0.5604</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.8028999999999999</v>
+        <v>-1.2301</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.2272</v>
+        <v>0.6829</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.0726</v>
+        <v>0.4261</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.347</v>
+        <v>0.3227</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2744</v>
+        <v>0.1035</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2507</v>
+        <v>-0.387</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2507</v>
+        <v>-0.387</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>C. DUARTE</t>
+          <t>O. BALCEROWSKI</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.6589</v>
+        <v>-0.9383</v>
       </c>
       <c r="E9" t="n">
-        <v>0.5097</v>
+        <v>1.4514</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.1686</v>
+        <v>-2.3897</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2036</v>
+        <v>-0.5123</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7416</v>
+        <v>-1.3841</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.462</v>
+        <v>0.8718</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5929</v>
+        <v>0.7055</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.178</v>
+        <v>-0.0764</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7709</v>
+        <v>0.782</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7965</v>
+        <v>-1.2179</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5635</v>
+        <v>-1.3077</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.2329</v>
+        <v>0.0898</v>
       </c>
       <c r="P9" t="n">
-        <v>0.6816</v>
+        <v>2.0487</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6816</v>
+        <v>2.0487</v>
       </c>
       <c r="S9" t="n">
-        <v>0.2494</v>
+        <v>0.6211</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3031</v>
+        <v>0.5732</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0537</v>
+        <v>0.0479</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3862</v>
+        <v>-3.0958</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3862</v>
+        <v>0.1726</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-3.2684</v>
       </c>
     </row>
     <row r="10">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6976</v>
+        <v>-1.3012</v>
       </c>
       <c r="E10" t="n">
-        <v>0.267</v>
+        <v>0.8571</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.9646</v>
+        <v>-2.1583</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.333</v>
+        <v>-0.3323</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.9881</v>
+        <v>-1.9874</v>
       </c>
       <c r="I10" t="n">
-        <v>1.655</v>
+        <v>1.6551</v>
       </c>
       <c r="J10" t="n">
-        <v>2.4929</v>
+        <v>2.4789</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7094</v>
+        <v>0.6992</v>
       </c>
       <c r="L10" t="n">
-        <v>1.7835</v>
+        <v>1.7797</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.8259</v>
+        <v>-2.8112</v>
       </c>
       <c r="N10" t="n">
-        <v>-2.6974</v>
+        <v>-2.6866</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.1285</v>
+        <v>-0.1246</v>
       </c>
       <c r="P10" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R10" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7958</v>
+        <v>-0.403</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.2493</v>
+        <v>-0.6415</v>
       </c>
       <c r="U10" t="n">
-        <v>0.4535</v>
+        <v>0.2385</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.4775</v>
+        <v>-1.4764</v>
       </c>
       <c r="W10" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.6369</v>
+        <v>-1.6342</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>T. KALINOSKI</t>
+          <t>J. COBBS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.0054</v>
+        <v>-2.1953</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.211</v>
+        <v>-1.5558</v>
       </c>
       <c r="F11" t="n">
-        <v>1.2056</v>
+        <v>-0.6395</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6444</v>
+        <v>-2.6003</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.5373</v>
+        <v>-0.3135</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.1071</v>
+        <v>-2.2868</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.0339</v>
+        <v>-1.1941</v>
       </c>
       <c r="K11" t="n">
-        <v>0.432</v>
+        <v>1.1376</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.466</v>
+        <v>-2.3317</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-1.4062</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9693000000000001</v>
+        <v>-1.4511</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3588</v>
+        <v>0.0449</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.8175</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.2719</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4544</v>
+        <v>0.9105</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0702</v>
+        <v>-0.2276</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0948</v>
+        <v>-0.0838</v>
       </c>
       <c r="U11" t="n">
-        <v>0.9754</v>
+        <v>-0.1438</v>
       </c>
       <c r="V11" t="n">
-        <v>0.3862</v>
+        <v>0.8603</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.8603</v>
       </c>
       <c r="X11" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>J. COBBS</t>
+          <t>T. KALINOSKI</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.611</v>
+        <v>-2.4178</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.085</v>
+        <v>-3.3875</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.526</v>
+        <v>0.9698</v>
       </c>
       <c r="G12" t="n">
-        <v>-2.6032</v>
+        <v>-1.6388</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.3171</v>
+        <v>-0.532</v>
       </c>
       <c r="I12" t="n">
-        <v>-2.2861</v>
+        <v>-1.1068</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.1889</v>
+        <v>-1.0367</v>
       </c>
       <c r="K12" t="n">
-        <v>1.1406</v>
+        <v>0.4309</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.3294</v>
+        <v>-1.4676</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.4144</v>
+        <v>-0.6022</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.4577</v>
+        <v>-0.9629</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0433</v>
+        <v>0.3608</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.2272</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q12" t="n">
-        <v>-1.1359</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>0.9087</v>
+        <v>0.4553</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.645</v>
+        <v>0.6551</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6247</v>
+        <v>-0.0746</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0203</v>
+        <v>0.7297</v>
       </c>
       <c r="V12" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.387</v>
       </c>
       <c r="W12" t="n">
-        <v>0.8643999999999999</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.9803</v>
+        <v>-4.3063</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.3104</v>
+        <v>-3.7761</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.67</v>
+        <v>-0.5302</v>
       </c>
       <c r="G13" t="n">
-        <v>-3.976</v>
+        <v>-3.9763</v>
       </c>
       <c r="H13" t="n">
-        <v>-4.0392</v>
+        <v>-4.0404</v>
       </c>
       <c r="I13" t="n">
-        <v>0.06320000000000001</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>-2.8499</v>
+        <v>-2.8582</v>
       </c>
       <c r="K13" t="n">
-        <v>-2.7694</v>
+        <v>-2.7761</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.0806</v>
+        <v>-0.08210000000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.126</v>
+        <v>-1.118</v>
       </c>
       <c r="N13" t="n">
-        <v>-1.2698</v>
+        <v>-1.2643</v>
       </c>
       <c r="O13" t="n">
-        <v>0.1438</v>
+        <v>0.1463</v>
       </c>
       <c r="P13" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q13" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R13" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S13" t="n">
-        <v>0.8597</v>
+        <v>0.5318000000000001</v>
       </c>
       <c r="T13" t="n">
-        <v>0.6755</v>
+        <v>0.2203</v>
       </c>
       <c r="U13" t="n">
-        <v>0.1842</v>
+        <v>0.3115</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-1.884400000000001</v>
+        <v>-0.4975999999999989</v>
       </c>
       <c r="E14" t="n">
-        <v>2.924500000000001</v>
+        <v>4.123200000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-4.809</v>
+        <v>-4.620699999999999</v>
       </c>
       <c r="G14" t="n">
-        <v>-4.536700000000001</v>
+        <v>-4.5338</v>
       </c>
       <c r="H14" t="n">
-        <v>-10.6318</v>
+        <v>-10.6264</v>
       </c>
       <c r="I14" t="n">
-        <v>6.094999999999999</v>
+        <v>6.092700000000001</v>
       </c>
       <c r="J14" t="n">
-        <v>13.0528</v>
+        <v>12.9475</v>
       </c>
       <c r="K14" t="n">
-        <v>4.0953</v>
+        <v>4.029400000000001</v>
       </c>
       <c r="L14" t="n">
-        <v>8.9573</v>
+        <v>8.918199999999999</v>
       </c>
       <c r="M14" t="n">
-        <v>-17.5895</v>
+        <v>-17.4816</v>
       </c>
       <c r="N14" t="n">
-        <v>-14.7268</v>
+        <v>-14.6557</v>
       </c>
       <c r="O14" t="n">
-        <v>-2.8626</v>
+        <v>-2.825499999999999</v>
       </c>
       <c r="P14" t="n">
-        <v>4.5438</v>
+        <v>4.552600000000001</v>
       </c>
       <c r="Q14" t="n">
-        <v>-12.4952</v>
+        <v>-12.5199</v>
       </c>
       <c r="R14" t="n">
-        <v>17.0391</v>
+        <v>17.0724</v>
       </c>
       <c r="S14" t="n">
-        <v>2.6513</v>
+        <v>4.040900000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5022</v>
+        <v>0.8552999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>3.1536</v>
+        <v>3.1854</v>
       </c>
       <c r="V14" t="n">
-        <v>-4.5426</v>
+        <v>-4.5573</v>
       </c>
       <c r="W14" t="n">
-        <v>2.8693</v>
+        <v>2.8398</v>
       </c>
       <c r="X14" t="n">
-        <v>-7.412100000000001</v>
+        <v>-7.397100000000001</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.5266</v>
+        <v>7.5458</v>
       </c>
       <c r="E15" t="n">
-        <v>7.5742</v>
+        <v>8.004099999999999</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0476</v>
+        <v>-0.4583</v>
       </c>
       <c r="G15" t="n">
-        <v>5.2239</v>
+        <v>5.2097</v>
       </c>
       <c r="H15" t="n">
-        <v>4.1174</v>
+        <v>4.108</v>
       </c>
       <c r="I15" t="n">
-        <v>1.1064</v>
+        <v>1.1018</v>
       </c>
       <c r="J15" t="n">
-        <v>6.6841</v>
+        <v>6.6549</v>
       </c>
       <c r="K15" t="n">
-        <v>5.3347</v>
+        <v>5.3155</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3494</v>
+        <v>1.3394</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.4602</v>
+        <v>-1.4451</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2173</v>
+        <v>-1.2075</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.243</v>
+        <v>-0.2377</v>
       </c>
       <c r="P15" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.3631</v>
+        <v>-1.3658</v>
       </c>
       <c r="R15" t="n">
-        <v>2.2719</v>
+        <v>2.2763</v>
       </c>
       <c r="S15" t="n">
-        <v>-2.1747</v>
+        <v>-1.1404</v>
       </c>
       <c r="T15" t="n">
-        <v>-1.1799</v>
+        <v>-0.7112000000000001</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9948</v>
+        <v>-0.4292</v>
       </c>
       <c r="V15" t="n">
-        <v>2.5687</v>
+        <v>2.5659</v>
       </c>
       <c r="W15" t="n">
-        <v>3.4332</v>
+        <v>3.4262</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>6.3082</v>
+        <v>6.0626</v>
       </c>
       <c r="E16" t="n">
-        <v>6.0357</v>
+        <v>6.0097</v>
       </c>
       <c r="F16" t="n">
-        <v>0.2725</v>
+        <v>0.0529</v>
       </c>
       <c r="G16" t="n">
-        <v>5.882</v>
+        <v>5.8757</v>
       </c>
       <c r="H16" t="n">
-        <v>3.496</v>
+        <v>3.4926</v>
       </c>
       <c r="I16" t="n">
-        <v>2.386</v>
+        <v>2.3832</v>
       </c>
       <c r="J16" t="n">
-        <v>6.7233</v>
+        <v>6.7024</v>
       </c>
       <c r="K16" t="n">
-        <v>3.7215</v>
+        <v>3.7092</v>
       </c>
       <c r="L16" t="n">
-        <v>3.0018</v>
+        <v>2.9932</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.8413</v>
+        <v>-0.8266</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.2255</v>
+        <v>-0.2166</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6158</v>
+        <v>-0.61</v>
       </c>
       <c r="P16" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="S16" t="n">
-        <v>0.155</v>
+        <v>-0.0926</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.4604</v>
+        <v>-0.465</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6155</v>
+        <v>0.3724</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6311</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6375999999999999</v>
+        <v>-0.6311</v>
       </c>
     </row>
     <row r="17">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9716</v>
+        <v>1.0056</v>
       </c>
       <c r="E17" t="n">
-        <v>1.0452</v>
+        <v>1.0424</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.0737</v>
+        <v>-0.0369</v>
       </c>
       <c r="G17" t="n">
-        <v>0.8817</v>
+        <v>0.882</v>
       </c>
       <c r="H17" t="n">
-        <v>0.7153</v>
+        <v>0.7151</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1664</v>
+        <v>0.1669</v>
       </c>
       <c r="J17" t="n">
-        <v>1.1841</v>
+        <v>1.1818</v>
       </c>
       <c r="K17" t="n">
-        <v>0.5876</v>
+        <v>0.5861</v>
       </c>
       <c r="L17" t="n">
-        <v>0.5965</v>
+        <v>0.5958</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.3023</v>
+        <v>-0.2998</v>
       </c>
       <c r="N17" t="n">
-        <v>0.1277</v>
+        <v>0.129</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.4301</v>
+        <v>-0.4289</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3641</v>
+        <v>-0.3333</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1388</v>
+        <v>-0.1394</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.2253</v>
+        <v>-0.1939</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2268</v>
+        <v>0.2292</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0.2268</v>
+        <v>0.2292</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>C. METU</t>
+          <t>C. ALOCEN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.8465</v>
+        <v>0.8456</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.091</v>
+        <v>0.8421999999999999</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9375</v>
+        <v>0.0034</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.6369</v>
+        <v>1.9913</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4245</v>
+        <v>1.8835</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2124</v>
+        <v>0.1078</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7268</v>
+        <v>2.9049</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5228</v>
+        <v>2.0857</v>
       </c>
       <c r="L18" t="n">
-        <v>1.2496</v>
+        <v>0.8192</v>
       </c>
       <c r="M18" t="n">
-        <v>-2.3636</v>
+        <v>-0.9136</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9016999999999999</v>
+        <v>-0.2022</v>
       </c>
       <c r="O18" t="n">
-        <v>-1.4619</v>
+        <v>-0.7114</v>
       </c>
       <c r="P18" t="n">
-        <v>0.2272</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.3631</v>
+        <v>-3.6421</v>
       </c>
       <c r="R18" t="n">
-        <v>1.5903</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.1657</v>
+        <v>-0.5931</v>
       </c>
       <c r="T18" t="n">
-        <v>-1.0915</v>
+        <v>-0.5995</v>
       </c>
       <c r="U18" t="n">
-        <v>1.2572</v>
+        <v>0.0065</v>
       </c>
       <c r="V18" t="n">
-        <v>2.0905</v>
+        <v>2.1789</v>
       </c>
       <c r="W18" t="n">
-        <v>1.6369</v>
+        <v>2.1789</v>
       </c>
       <c r="X18" t="n">
-        <v>0.4536</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. ALOCEN</t>
+          <t>C. METU</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.8277</v>
+        <v>0.6096</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6258</v>
+        <v>0.2348</v>
       </c>
       <c r="F19" t="n">
-        <v>0.2018</v>
+        <v>0.3749</v>
       </c>
       <c r="G19" t="n">
-        <v>1.9844</v>
+        <v>-1.6401</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8806</v>
+        <v>-1.4269</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1039</v>
+        <v>-0.2131</v>
       </c>
       <c r="J19" t="n">
-        <v>2.9112</v>
+        <v>0.7077</v>
       </c>
       <c r="K19" t="n">
-        <v>2.091</v>
+        <v>-0.5353</v>
       </c>
       <c r="L19" t="n">
-        <v>0.8202</v>
+        <v>1.243</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9268</v>
+        <v>-2.3478</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2104</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7163</v>
+        <v>-1.4562</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.7262</v>
+        <v>0.2276</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.635</v>
+        <v>-1.3658</v>
       </c>
       <c r="R19" t="n">
-        <v>0.9087</v>
+        <v>1.5934</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.613</v>
+        <v>-0.0706</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.8329</v>
+        <v>-0.7413999999999999</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2198</v>
+        <v>0.6708</v>
       </c>
       <c r="V19" t="n">
-        <v>2.1825</v>
+        <v>2.0926</v>
       </c>
       <c r="W19" t="n">
-        <v>2.1825</v>
+        <v>1.6342</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>0.4584</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>N. BRUSSINO</t>
+          <t>L. MANIEMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6189</v>
+        <v>0.1579</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6221</v>
+        <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0032</v>
+        <v>0.1579</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7395</v>
+        <v>0.1579</v>
       </c>
       <c r="H20" t="n">
-        <v>1.3509</v>
+        <v>0</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.0904</v>
+        <v>0.1579</v>
       </c>
       <c r="J20" t="n">
-        <v>2.0542</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>2.2526</v>
+        <v>0</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.1984</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.7937</v>
+        <v>0.1579</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9016999999999999</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.892</v>
+        <v>0.1579</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.2272</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.4991</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.2719</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9726</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.0669</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0944</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
-        <v>0.613</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.613</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>L. MANIEMA</t>
+          <t>N. BRUSSINO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.1578</v>
+        <v>-0.219</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>-0.4643</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1578</v>
+        <v>0.2453</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1578</v>
+        <v>-0.7342</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>1.3524</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1578</v>
+        <v>-2.0866</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>2.0425</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>2.244</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.2015</v>
       </c>
       <c r="M21" t="n">
-        <v>0.1578</v>
+        <v>-2.7767</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>-0.8915999999999999</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1578</v>
+        <v>-1.8851</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-2.5039</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.2763</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>0.1266</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-0.0029</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.1295</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>0.6162</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="22">
@@ -2125,58 +2125,58 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.6042</v>
+        <v>-0.4794</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.2002</v>
+        <v>-1.2031</v>
       </c>
       <c r="F22" t="n">
-        <v>0.596</v>
+        <v>0.7237</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6756</v>
+        <v>0.6773</v>
       </c>
       <c r="H22" t="n">
-        <v>0.2855</v>
+        <v>0.287</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3901</v>
+        <v>0.3903</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="K22" t="n">
         <v>0</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0746</v>
+        <v>0.0745</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6011</v>
+        <v>0.6028</v>
       </c>
       <c r="N22" t="n">
-        <v>0.2855</v>
+        <v>0.287</v>
       </c>
       <c r="O22" t="n">
-        <v>0.3156</v>
+        <v>0.3159</v>
       </c>
       <c r="P22" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.1439</v>
+        <v>-0.0185</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1388</v>
+        <v>-0.1394</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.0051</v>
+        <v>0.1209</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.2299</v>
+        <v>-2.1163</v>
       </c>
       <c r="E23" t="n">
-        <v>1.2883</v>
+        <v>0.5657</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5182</v>
+        <v>-2.682</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.6673</v>
+        <v>-0.6647</v>
       </c>
       <c r="H23" t="n">
         <v>0.4538</v>
       </c>
       <c r="I23" t="n">
-        <v>-1.1211</v>
+        <v>-1.1184</v>
       </c>
       <c r="J23" t="n">
-        <v>1.3621</v>
+        <v>1.356</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2503</v>
+        <v>1.2443</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.0294</v>
+        <v>-2.0207</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.7965</v>
+        <v>-0.7906</v>
       </c>
       <c r="O23" t="n">
-        <v>-1.2329</v>
+        <v>-1.2301</v>
       </c>
       <c r="P23" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S23" t="n">
-        <v>1.2572</v>
+        <v>0.36</v>
       </c>
       <c r="T23" t="n">
-        <v>0.9026999999999999</v>
+        <v>0.1901</v>
       </c>
       <c r="U23" t="n">
-        <v>0.3545</v>
+        <v>0.1699</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.5013</v>
+        <v>-2.4945</v>
       </c>
       <c r="W23" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.6607</v>
+        <v>-2.6522</v>
       </c>
     </row>
     <row r="24">
@@ -2281,58 +2281,58 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.3528</v>
+        <v>-2.9072</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.3014</v>
+        <v>-2.8378</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.0514</v>
+        <v>-0.06950000000000001</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1266</v>
+        <v>-2.1209</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.142</v>
+        <v>-0.1384</v>
       </c>
       <c r="I24" t="n">
-        <v>-1.9846</v>
+        <v>-1.9825</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.285</v>
+        <v>-0.287</v>
       </c>
       <c r="K24" t="n">
-        <v>0.4666</v>
+        <v>0.4654</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.7516</v>
+        <v>-0.7524</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.8416</v>
+        <v>-1.8339</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.6086</v>
+        <v>-0.6037</v>
       </c>
       <c r="O24" t="n">
-        <v>-1.2329</v>
+        <v>-1.2301</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.6816</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5446</v>
+        <v>-0.1035</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.7445000000000001</v>
+        <v>-0.2744</v>
       </c>
       <c r="U24" t="n">
-        <v>0.1999</v>
+        <v>0.171</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,58 +2359,58 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-9.186</v>
+        <v>-8.6135</v>
       </c>
       <c r="E25" t="n">
-        <v>-7.7899</v>
+        <v>-7.5729</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.3961</v>
+        <v>-1.0406</v>
       </c>
       <c r="G25" t="n">
-        <v>-5.0985</v>
+        <v>-5.1004</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.1014</v>
+        <v>-0.1006</v>
       </c>
       <c r="I25" t="n">
-        <v>-4.997</v>
+        <v>-4.9998</v>
       </c>
       <c r="J25" t="n">
-        <v>-3.8458</v>
+        <v>-3.8562</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.4545</v>
+        <v>-0.4589</v>
       </c>
       <c r="L25" t="n">
-        <v>-3.3913</v>
+        <v>-3.3973</v>
       </c>
       <c r="M25" t="n">
-        <v>-1.2527</v>
+        <v>-1.2442</v>
       </c>
       <c r="N25" t="n">
-        <v>0.3531</v>
+        <v>0.3583</v>
       </c>
       <c r="O25" t="n">
-        <v>-1.6058</v>
+        <v>-1.6025</v>
       </c>
       <c r="P25" t="n">
-        <v>-2.7262</v>
+        <v>-2.7316</v>
       </c>
       <c r="Q25" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R25" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.3613</v>
+        <v>-0.7815</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5363</v>
+        <v>-0.3022</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.825</v>
+        <v>-0.4793</v>
       </c>
       <c r="V25" t="n">
         <v>0</v>
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>1.884399999999999</v>
+        <v>1.891700000000002</v>
       </c>
       <c r="E26" t="n">
-        <v>4.808800000000001</v>
+        <v>4.620799999999998</v>
       </c>
       <c r="F26" t="n">
-        <v>-2.9246</v>
+        <v>-2.7292</v>
       </c>
       <c r="G26" t="n">
-        <v>4.536599999999998</v>
+        <v>4.533600000000001</v>
       </c>
       <c r="H26" t="n">
-        <v>10.6316</v>
+        <v>10.6265</v>
       </c>
       <c r="I26" t="n">
-        <v>-6.094899999999999</v>
+        <v>-6.092499999999999</v>
       </c>
       <c r="J26" t="n">
-        <v>17.5896</v>
+        <v>17.4815</v>
       </c>
       <c r="K26" t="n">
-        <v>14.727</v>
+        <v>14.656</v>
       </c>
       <c r="L26" t="n">
-        <v>2.862599999999999</v>
+        <v>2.8256</v>
       </c>
       <c r="M26" t="n">
-        <v>-13.0527</v>
+        <v>-12.9477</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.0954</v>
+        <v>-4.029500000000001</v>
       </c>
       <c r="O26" t="n">
-        <v>-8.9573</v>
+        <v>-8.918199999999999</v>
       </c>
       <c r="P26" t="n">
-        <v>-4.543699999999999</v>
+        <v>-4.5528</v>
       </c>
       <c r="Q26" t="n">
-        <v>-17.039</v>
+        <v>-17.0724</v>
       </c>
       <c r="R26" t="n">
-        <v>12.4953</v>
+        <v>12.5197</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.6511</v>
+        <v>-2.6469</v>
       </c>
       <c r="T26" t="n">
-        <v>-3.153499999999999</v>
+        <v>-3.1853</v>
       </c>
       <c r="U26" t="n">
-        <v>0.5023000000000002</v>
+        <v>0.5386</v>
       </c>
       <c r="V26" t="n">
-        <v>4.5426</v>
+        <v>4.5572</v>
       </c>
       <c r="W26" t="n">
-        <v>7.412</v>
+        <v>7.3971</v>
       </c>
       <c r="X26" t="n">
-        <v>-2.8693</v>
+        <v>-2.8398</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104727_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104727_W30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>0</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-3.2684</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-1.6342</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>0</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,11 @@
       <c r="X13" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1628,7 @@
       <c r="X14" t="n">
         <v>-7.397100000000001</v>
       </c>
+      <c r="Y14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.6311</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0.2292</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>0</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0.4584</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>0</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>0</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-2.6522</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>0</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104727_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-2.8398</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
